--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ144"/>
+  <dimension ref="A1:AZ146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128388173</v>
+        <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>78993</v>
+        <v>79506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470786</v>
+        <v>470924</v>
       </c>
       <c r="R22" t="n">
-        <v>6866737</v>
+        <v>6866714</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,13 +2816,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388173</t>
+          <t>https://artportalen.se/Sighting/136684899</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128502518</v>
+        <v>128388173</v>
       </c>
       <c r="B23" t="n">
         <v>78993</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471323</v>
+        <v>470786</v>
       </c>
       <c r="R23" t="n">
-        <v>6866655</v>
+        <v>6866737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,13 +2918,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502518</t>
+          <t>https://artportalen.se/Sighting/128388173</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129012527</v>
+        <v>128502518</v>
       </c>
       <c r="B24" t="n">
         <v>78993</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470886</v>
+        <v>471323</v>
       </c>
       <c r="R24" t="n">
-        <v>6866737</v>
+        <v>6866655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,60 +3020,51 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129012527</t>
+          <t>https://artportalen.se/Sighting/128502518</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128376462</v>
+        <v>129012527</v>
       </c>
       <c r="B25" t="n">
-        <v>92509</v>
+        <v>78993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471351</v>
+        <v>470886</v>
       </c>
       <c r="R25" t="n">
-        <v>6866748</v>
+        <v>6866737</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,17 +3091,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,51 +3122,60 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376462</t>
+          <t>https://artportalen.se/Sighting/129012527</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128388766</v>
+        <v>128376462</v>
       </c>
       <c r="B26" t="n">
-        <v>79406</v>
+        <v>92509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470981</v>
+        <v>471351</v>
       </c>
       <c r="R26" t="n">
-        <v>6866714</v>
+        <v>6866748</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,12 +3202,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fyra fruktkroppar på stående sälg och fyra dito på liggande död del av sälgen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3238,13 +3238,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388766</t>
+          <t>https://artportalen.se/Sighting/128376462</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128388778</v>
+        <v>128388766</v>
       </c>
       <c r="B27" t="n">
         <v>79406</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470995</v>
+        <v>470981</v>
       </c>
       <c r="R27" t="n">
-        <v>6866711</v>
+        <v>6866714</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,16 +3340,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388778</t>
+          <t>https://artportalen.se/Sighting/128388766</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128374859</v>
+        <v>128388778</v>
       </c>
       <c r="B28" t="n">
-        <v>80433</v>
+        <v>79406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,21 +3357,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471125</v>
+        <v>470995</v>
       </c>
       <c r="R28" t="n">
-        <v>6866815</v>
+        <v>6866711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3442,13 +3442,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374859</t>
+          <t>https://artportalen.se/Sighting/128388778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128388953</v>
+        <v>128374859</v>
       </c>
       <c r="B29" t="n">
         <v>80433</v>
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471080</v>
+        <v>471125</v>
       </c>
       <c r="R29" t="n">
-        <v>6866746</v>
+        <v>6866815</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3544,13 +3544,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388953</t>
+          <t>https://artportalen.se/Sighting/128374859</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128389262</v>
+        <v>128388953</v>
       </c>
       <c r="B30" t="n">
         <v>80433</v>
@@ -3585,13 +3585,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471168</v>
+        <v>471080</v>
       </c>
       <c r="R30" t="n">
-        <v>6866647</v>
+        <v>6866746</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3646,13 +3646,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389262</t>
+          <t>https://artportalen.se/Sighting/128388953</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128389587</v>
+        <v>128389262</v>
       </c>
       <c r="B31" t="n">
         <v>80433</v>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471274</v>
+        <v>471168</v>
       </c>
       <c r="R31" t="n">
-        <v>6866626</v>
+        <v>6866647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,13 +3748,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389587</t>
+          <t>https://artportalen.se/Sighting/128389262</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129010706</v>
+        <v>128389587</v>
       </c>
       <c r="B32" t="n">
         <v>80433</v>
@@ -3785,14 +3785,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillhamra, Lillhamra, Hjd</t>
+          <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>471062</v>
+        <v>471274</v>
       </c>
       <c r="R32" t="n">
-        <v>6866859</v>
+        <v>6866626</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3850,16 +3850,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129010706</t>
+          <t>https://artportalen.se/Sighting/128389587</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011154</v>
+        <v>129010706</v>
       </c>
       <c r="B33" t="n">
-        <v>93197</v>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3867,48 +3867,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sålnberget, Sålnberget, Hjd</t>
+          <t>Lillhamra, Lillhamra, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471298</v>
+        <v>471062</v>
       </c>
       <c r="R33" t="n">
-        <v>6866571</v>
+        <v>6866859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3966,13 +3952,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011154</t>
+          <t>https://artportalen.se/Sighting/129010706</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011818</v>
+        <v>129011154</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4010,16 +3996,21 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471292</v>
+        <v>471298</v>
       </c>
       <c r="R34" t="n">
-        <v>6866776</v>
+        <v>6866571</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4077,16 +4068,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011818</t>
+          <t>https://artportalen.se/Sighting/129011154</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011146</v>
+        <v>129011818</v>
       </c>
       <c r="B35" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4094,34 +4085,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471277</v>
+        <v>471292</v>
       </c>
       <c r="R35" t="n">
-        <v>6866584</v>
+        <v>6866776</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,54 +4179,68 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011146</t>
+          <t>https://artportalen.se/Sighting/129011818</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128502704</v>
+        <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>93403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471366</v>
+        <v>470766</v>
       </c>
       <c r="R36" t="n">
-        <v>6866720</v>
+        <v>6866728</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4250,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4281,16 +4295,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502704</t>
+          <t>https://artportalen.se/Sighting/136684295</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011121</v>
+        <v>129011146</v>
       </c>
       <c r="B37" t="n">
-        <v>93235</v>
+        <v>93209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,48 +4312,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471276</v>
+        <v>471277</v>
       </c>
       <c r="R37" t="n">
-        <v>6866578</v>
+        <v>6866584</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4397,38 +4397,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011121</t>
+          <t>https://artportalen.se/Sighting/129011146</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128373888</v>
+        <v>128502704</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471081</v>
+        <v>471366</v>
       </c>
       <c r="R38" t="n">
-        <v>6866883</v>
+        <v>6866720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4499,51 +4499,65 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128373888</t>
+          <t>https://artportalen.se/Sighting/128502704</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128374116</v>
+        <v>129011121</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471107</v>
+        <v>471276</v>
       </c>
       <c r="R39" t="n">
-        <v>6866853</v>
+        <v>6866578</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,12 +4584,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4601,13 +4615,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374116</t>
+          <t>https://artportalen.se/Sighting/129011121</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128374452</v>
+        <v>128373888</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4642,10 +4656,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>471138</v>
+        <v>471081</v>
       </c>
       <c r="R40" t="n">
-        <v>6866841</v>
+        <v>6866883</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,13 +4717,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374452</t>
+          <t>https://artportalen.se/Sighting/128373888</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128374662</v>
+        <v>128374116</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -4744,10 +4758,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471145</v>
+        <v>471107</v>
       </c>
       <c r="R41" t="n">
-        <v>6866824</v>
+        <v>6866853</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,13 +4819,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374662</t>
+          <t>https://artportalen.se/Sighting/128374116</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128374814</v>
+        <v>128374452</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -4846,10 +4860,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471137</v>
+        <v>471138</v>
       </c>
       <c r="R42" t="n">
-        <v>6866828</v>
+        <v>6866841</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4884,11 +4898,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4912,13 +4921,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374814</t>
+          <t>https://artportalen.se/Sighting/128374452</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128375168</v>
+        <v>128374662</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -4953,10 +4962,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471139</v>
+        <v>471145</v>
       </c>
       <c r="R43" t="n">
-        <v>6866821</v>
+        <v>6866824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,13 +5023,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375168</t>
+          <t>https://artportalen.se/Sighting/128374662</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128375190</v>
+        <v>128374814</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5055,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471145</v>
+        <v>471137</v>
       </c>
       <c r="R44" t="n">
-        <v>6866802</v>
+        <v>6866828</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,6 +5102,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5116,13 +5130,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375190</t>
+          <t>https://artportalen.se/Sighting/128374814</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128375214</v>
+        <v>128375168</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5157,10 +5171,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471144</v>
+        <v>471139</v>
       </c>
       <c r="R45" t="n">
-        <v>6866814</v>
+        <v>6866821</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,13 +5232,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375214</t>
+          <t>https://artportalen.se/Sighting/128375168</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128375249</v>
+        <v>128375190</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5259,10 +5273,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471158</v>
+        <v>471145</v>
       </c>
       <c r="R46" t="n">
-        <v>6866800</v>
+        <v>6866802</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,13 +5334,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375249</t>
+          <t>https://artportalen.se/Sighting/128375190</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128375289</v>
+        <v>128375214</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5361,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>471165</v>
+        <v>471144</v>
       </c>
       <c r="R47" t="n">
-        <v>6866794</v>
+        <v>6866814</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,13 +5436,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375289</t>
+          <t>https://artportalen.se/Sighting/128375214</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128375307</v>
+        <v>128375249</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5463,10 +5477,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471169</v>
+        <v>471158</v>
       </c>
       <c r="R48" t="n">
-        <v>6866788</v>
+        <v>6866800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,13 +5538,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375307</t>
+          <t>https://artportalen.se/Sighting/128375249</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128375358</v>
+        <v>128375289</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5565,10 +5579,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471166</v>
+        <v>471165</v>
       </c>
       <c r="R49" t="n">
-        <v>6866785</v>
+        <v>6866794</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,13 +5640,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375358</t>
+          <t>https://artportalen.se/Sighting/128375289</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128375399</v>
+        <v>128375307</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5667,10 +5681,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R50" t="n">
-        <v>6866790</v>
+        <v>6866788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,13 +5742,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375399</t>
+          <t>https://artportalen.se/Sighting/128375307</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128375464</v>
+        <v>128375358</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5769,10 +5783,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>471186</v>
+        <v>471166</v>
       </c>
       <c r="R51" t="n">
-        <v>6866787</v>
+        <v>6866785</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,13 +5844,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375464</t>
+          <t>https://artportalen.se/Sighting/128375358</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128375498</v>
+        <v>128375399</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -5871,10 +5885,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>471198</v>
+        <v>471183</v>
       </c>
       <c r="R52" t="n">
-        <v>6866776</v>
+        <v>6866790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,13 +5946,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375498</t>
+          <t>https://artportalen.se/Sighting/128375399</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128375508</v>
+        <v>128375464</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -5973,10 +5987,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471209</v>
+        <v>471186</v>
       </c>
       <c r="R53" t="n">
-        <v>6866776</v>
+        <v>6866787</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,13 +6048,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375508</t>
+          <t>https://artportalen.se/Sighting/128375464</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128375734</v>
+        <v>128375498</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6075,13 +6089,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471234</v>
+        <v>471198</v>
       </c>
       <c r="R54" t="n">
-        <v>6866765</v>
+        <v>6866776</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6136,13 +6150,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375734</t>
+          <t>https://artportalen.se/Sighting/128375498</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128375758</v>
+        <v>128375508</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6177,10 +6191,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>471232</v>
+        <v>471209</v>
       </c>
       <c r="R55" t="n">
-        <v>6866781</v>
+        <v>6866776</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,13 +6252,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375758</t>
+          <t>https://artportalen.se/Sighting/128375508</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128375808</v>
+        <v>128375734</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6279,13 +6293,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>471247</v>
+        <v>471234</v>
       </c>
       <c r="R56" t="n">
-        <v>6866787</v>
+        <v>6866765</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6340,13 +6354,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375808</t>
+          <t>https://artportalen.se/Sighting/128375734</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128375959</v>
+        <v>128375758</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6381,10 +6395,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>471266</v>
+        <v>471232</v>
       </c>
       <c r="R57" t="n">
-        <v>6866792</v>
+        <v>6866781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,13 +6456,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375959</t>
+          <t>https://artportalen.se/Sighting/128375758</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128376206</v>
+        <v>128375808</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6483,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>471275</v>
+        <v>471247</v>
       </c>
       <c r="R58" t="n">
-        <v>6866797</v>
+        <v>6866787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,13 +6558,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376206</t>
+          <t>https://artportalen.se/Sighting/128375808</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128376258</v>
+        <v>128375959</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6585,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471292</v>
+        <v>471266</v>
       </c>
       <c r="R59" t="n">
-        <v>6866805</v>
+        <v>6866792</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,13 +6660,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376258</t>
+          <t>https://artportalen.se/Sighting/128375959</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128376295</v>
+        <v>128376206</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -6687,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471321</v>
+        <v>471275</v>
       </c>
       <c r="R60" t="n">
-        <v>6866820</v>
+        <v>6866797</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,13 +6762,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376295</t>
+          <t>https://artportalen.se/Sighting/128376206</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128376373</v>
+        <v>128376258</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -6789,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>471330</v>
+        <v>471292</v>
       </c>
       <c r="R61" t="n">
-        <v>6866787</v>
+        <v>6866805</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,13 +6864,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376373</t>
+          <t>https://artportalen.se/Sighting/128376258</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128376382</v>
+        <v>128376295</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -6891,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>471342</v>
+        <v>471321</v>
       </c>
       <c r="R62" t="n">
-        <v>6866780</v>
+        <v>6866820</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,13 +6966,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376382</t>
+          <t>https://artportalen.se/Sighting/128376295</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128376618</v>
+        <v>128376373</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -6993,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471331</v>
+        <v>471330</v>
       </c>
       <c r="R63" t="n">
-        <v>6866715</v>
+        <v>6866787</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,13 +7068,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376618</t>
+          <t>https://artportalen.se/Sighting/128376373</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128376636</v>
+        <v>128376382</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7095,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471320</v>
+        <v>471342</v>
       </c>
       <c r="R64" t="n">
-        <v>6866734</v>
+        <v>6866780</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7156,13 +7170,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376636</t>
+          <t>https://artportalen.se/Sighting/128376382</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128376649</v>
+        <v>128376618</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7197,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471300</v>
+        <v>471331</v>
       </c>
       <c r="R65" t="n">
-        <v>6866735</v>
+        <v>6866715</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7258,13 +7272,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376649</t>
+          <t>https://artportalen.se/Sighting/128376618</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128376676</v>
+        <v>128376636</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7299,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471287</v>
+        <v>471320</v>
       </c>
       <c r="R66" t="n">
-        <v>6866763</v>
+        <v>6866734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7360,13 +7374,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376676</t>
+          <t>https://artportalen.se/Sighting/128376636</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128388496</v>
+        <v>128376649</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -7401,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470869</v>
+        <v>471300</v>
       </c>
       <c r="R67" t="n">
-        <v>6866723</v>
+        <v>6866735</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7431,12 +7445,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7462,13 +7476,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388496</t>
+          <t>https://artportalen.se/Sighting/128376649</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128388690</v>
+        <v>128376676</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7503,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470982</v>
+        <v>471287</v>
       </c>
       <c r="R68" t="n">
-        <v>6866703</v>
+        <v>6866763</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7533,12 +7547,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7564,13 +7578,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388690</t>
+          <t>https://artportalen.se/Sighting/128376676</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128388714</v>
+        <v>128388496</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7605,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470987</v>
+        <v>470869</v>
       </c>
       <c r="R69" t="n">
-        <v>6866714</v>
+        <v>6866723</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7666,13 +7680,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388714</t>
+          <t>https://artportalen.se/Sighting/128388496</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128388815</v>
+        <v>128388690</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -7707,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470992</v>
+        <v>470982</v>
       </c>
       <c r="R70" t="n">
-        <v>6866696</v>
+        <v>6866703</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7768,13 +7782,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388815</t>
+          <t>https://artportalen.se/Sighting/128388690</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128388996</v>
+        <v>128388714</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -7809,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471118</v>
+        <v>470987</v>
       </c>
       <c r="R71" t="n">
-        <v>6866746</v>
+        <v>6866714</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7870,13 +7884,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388996</t>
+          <t>https://artportalen.se/Sighting/128388714</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128389124</v>
+        <v>128388815</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -7911,13 +7925,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471167</v>
+        <v>470992</v>
       </c>
       <c r="R72" t="n">
-        <v>6866694</v>
+        <v>6866696</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7972,13 +7986,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389124</t>
+          <t>https://artportalen.se/Sighting/128388815</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128389886</v>
+        <v>128388996</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8013,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471211</v>
+        <v>471118</v>
       </c>
       <c r="R73" t="n">
-        <v>6866717</v>
+        <v>6866746</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8074,13 +8088,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389886</t>
+          <t>https://artportalen.se/Sighting/128388996</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128389894</v>
+        <v>128389124</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8115,13 +8129,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471207</v>
+        <v>471167</v>
       </c>
       <c r="R74" t="n">
-        <v>6866729</v>
+        <v>6866694</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8176,13 +8190,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389894</t>
+          <t>https://artportalen.se/Sighting/128389124</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128389901</v>
+        <v>128389886</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8217,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471209</v>
+        <v>471211</v>
       </c>
       <c r="R75" t="n">
-        <v>6866743</v>
+        <v>6866717</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8278,13 +8292,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389901</t>
+          <t>https://artportalen.se/Sighting/128389886</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128389918</v>
+        <v>128389894</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8319,13 +8333,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471210</v>
+        <v>471207</v>
       </c>
       <c r="R76" t="n">
-        <v>6866755</v>
+        <v>6866729</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8380,13 +8394,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389918</t>
+          <t>https://artportalen.se/Sighting/128389894</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128389953</v>
+        <v>128389901</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8421,13 +8435,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471200</v>
+        <v>471209</v>
       </c>
       <c r="R77" t="n">
-        <v>6866759</v>
+        <v>6866743</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8482,13 +8496,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389953</t>
+          <t>https://artportalen.se/Sighting/128389901</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128501097</v>
+        <v>128389918</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8523,13 +8537,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471224</v>
+        <v>471210</v>
       </c>
       <c r="R78" t="n">
-        <v>6866707</v>
+        <v>6866755</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8553,12 +8567,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8584,13 +8598,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501097</t>
+          <t>https://artportalen.se/Sighting/128389918</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128501127</v>
+        <v>128389953</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8625,13 +8639,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471245</v>
+        <v>471200</v>
       </c>
       <c r="R79" t="n">
-        <v>6866708</v>
+        <v>6866759</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8655,12 +8669,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8686,13 +8700,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501127</t>
+          <t>https://artportalen.se/Sighting/128389953</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128501140</v>
+        <v>128501097</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8727,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471253</v>
+        <v>471224</v>
       </c>
       <c r="R80" t="n">
-        <v>6866704</v>
+        <v>6866707</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,13 +8802,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501140</t>
+          <t>https://artportalen.se/Sighting/128501097</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128501181</v>
+        <v>128501127</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -8829,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471251</v>
+        <v>471245</v>
       </c>
       <c r="R81" t="n">
-        <v>6866689</v>
+        <v>6866708</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8890,13 +8904,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501181</t>
+          <t>https://artportalen.se/Sighting/128501127</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128501794</v>
+        <v>128501140</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -8931,13 +8945,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471329</v>
+        <v>471253</v>
       </c>
       <c r="R82" t="n">
-        <v>6866557</v>
+        <v>6866704</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8992,13 +9006,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501794</t>
+          <t>https://artportalen.se/Sighting/128501140</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128502178</v>
+        <v>128501181</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9033,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471326</v>
+        <v>471251</v>
       </c>
       <c r="R83" t="n">
-        <v>6866583</v>
+        <v>6866689</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9094,13 +9108,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502178</t>
+          <t>https://artportalen.se/Sighting/128501181</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128502212</v>
+        <v>128501794</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9135,13 +9149,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471325</v>
+        <v>471329</v>
       </c>
       <c r="R84" t="n">
-        <v>6866592</v>
+        <v>6866557</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9196,13 +9210,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502212</t>
+          <t>https://artportalen.se/Sighting/128501794</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128502263</v>
+        <v>128502178</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9237,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471328</v>
+        <v>471326</v>
       </c>
       <c r="R85" t="n">
-        <v>6866612</v>
+        <v>6866583</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9298,13 +9312,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502263</t>
+          <t>https://artportalen.se/Sighting/128502178</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128502802</v>
+        <v>128502212</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9339,10 +9353,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471256</v>
+        <v>471325</v>
       </c>
       <c r="R86" t="n">
-        <v>6866728</v>
+        <v>6866592</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9400,38 +9414,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502802</t>
+          <t>https://artportalen.se/Sighting/128502212</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128376702</v>
+        <v>128502263</v>
       </c>
       <c r="B87" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9441,13 +9455,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471287</v>
+        <v>471328</v>
       </c>
       <c r="R87" t="n">
-        <v>6866773</v>
+        <v>6866612</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9471,12 +9485,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9502,38 +9516,38 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376702</t>
+          <t>https://artportalen.se/Sighting/128502263</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128374470</v>
+        <v>128502802</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9543,10 +9557,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471139</v>
+        <v>471256</v>
       </c>
       <c r="R88" t="n">
-        <v>6866835</v>
+        <v>6866728</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9573,12 +9587,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9604,16 +9618,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374470</t>
+          <t>https://artportalen.se/Sighting/128502802</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128388207</v>
+        <v>128376702</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9621,21 +9635,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9645,13 +9659,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>470789</v>
+        <v>471287</v>
       </c>
       <c r="R89" t="n">
-        <v>6866739</v>
+        <v>6866773</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9675,12 +9689,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9706,13 +9720,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388207</t>
+          <t>https://artportalen.se/Sighting/128376702</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128389187</v>
+        <v>128374470</v>
       </c>
       <c r="B90" t="n">
         <v>79084</v>
@@ -9747,10 +9761,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471196</v>
+        <v>471139</v>
       </c>
       <c r="R90" t="n">
-        <v>6866706</v>
+        <v>6866835</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9777,12 +9791,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9808,13 +9822,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389187</t>
+          <t>https://artportalen.se/Sighting/128374470</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128389329</v>
+        <v>128388207</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -9849,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471172</v>
+        <v>470789</v>
       </c>
       <c r="R91" t="n">
-        <v>6866632</v>
+        <v>6866739</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9910,13 +9924,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389329</t>
+          <t>https://artportalen.se/Sighting/128388207</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128501083</v>
+        <v>128389187</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -9951,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471219</v>
+        <v>471196</v>
       </c>
       <c r="R92" t="n">
-        <v>6866725</v>
+        <v>6866706</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9981,12 +9995,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10012,13 +10026,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501083</t>
+          <t>https://artportalen.se/Sighting/128389187</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128501209</v>
+        <v>128389329</v>
       </c>
       <c r="B93" t="n">
         <v>79084</v>
@@ -10053,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471244</v>
+        <v>471172</v>
       </c>
       <c r="R93" t="n">
-        <v>6866687</v>
+        <v>6866632</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10083,12 +10097,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10114,13 +10128,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501209</t>
+          <t>https://artportalen.se/Sighting/128389329</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128502509</v>
+        <v>128501083</v>
       </c>
       <c r="B94" t="n">
         <v>79084</v>
@@ -10155,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471315</v>
+        <v>471219</v>
       </c>
       <c r="R94" t="n">
-        <v>6866670</v>
+        <v>6866725</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10216,13 +10230,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502509</t>
+          <t>https://artportalen.se/Sighting/128501083</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128502607</v>
+        <v>128501209</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -10257,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471349</v>
+        <v>471244</v>
       </c>
       <c r="R95" t="n">
-        <v>6866695</v>
+        <v>6866687</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10318,16 +10332,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502607</t>
+          <t>https://artportalen.se/Sighting/128501209</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128373940</v>
+        <v>128502509</v>
       </c>
       <c r="B96" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10335,21 +10349,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10359,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471083</v>
+        <v>471315</v>
       </c>
       <c r="R96" t="n">
-        <v>6866852</v>
+        <v>6866670</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10389,12 +10403,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10420,16 +10434,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128373940</t>
+          <t>https://artportalen.se/Sighting/128502509</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128373989</v>
+        <v>128502607</v>
       </c>
       <c r="B97" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10437,21 +10451,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10461,10 +10475,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471102</v>
+        <v>471349</v>
       </c>
       <c r="R97" t="n">
-        <v>6866857</v>
+        <v>6866695</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10491,12 +10505,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10522,13 +10536,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128373989</t>
+          <t>https://artportalen.se/Sighting/128502607</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128387227</v>
+        <v>128373940</v>
       </c>
       <c r="B98" t="n">
         <v>80432</v>
@@ -10563,10 +10577,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470551</v>
+        <v>471083</v>
       </c>
       <c r="R98" t="n">
-        <v>6866892</v>
+        <v>6866852</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10593,12 +10607,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10624,13 +10638,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387227</t>
+          <t>https://artportalen.se/Sighting/128373940</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128387286</v>
+        <v>128373989</v>
       </c>
       <c r="B99" t="n">
         <v>80432</v>
@@ -10665,10 +10679,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>470551</v>
+        <v>471102</v>
       </c>
       <c r="R99" t="n">
-        <v>6866872</v>
+        <v>6866857</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,12 +10709,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10726,13 +10740,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387286</t>
+          <t>https://artportalen.se/Sighting/128373989</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128387292</v>
+        <v>128387227</v>
       </c>
       <c r="B100" t="n">
         <v>80432</v>
@@ -10770,7 +10784,7 @@
         <v>470551</v>
       </c>
       <c r="R100" t="n">
-        <v>6866868</v>
+        <v>6866892</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10828,13 +10842,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387292</t>
+          <t>https://artportalen.se/Sighting/128387227</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128387487</v>
+        <v>128387286</v>
       </c>
       <c r="B101" t="n">
         <v>80432</v>
@@ -10869,13 +10883,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>470706</v>
+        <v>470551</v>
       </c>
       <c r="R101" t="n">
-        <v>6866759</v>
+        <v>6866872</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10930,13 +10944,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387487</t>
+          <t>https://artportalen.se/Sighting/128387286</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128387736</v>
+        <v>128387292</v>
       </c>
       <c r="B102" t="n">
         <v>80432</v>
@@ -10971,10 +10985,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>470738</v>
+        <v>470551</v>
       </c>
       <c r="R102" t="n">
-        <v>6866733</v>
+        <v>6866868</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11032,13 +11046,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387736</t>
+          <t>https://artportalen.se/Sighting/128387292</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128389069</v>
+        <v>128387487</v>
       </c>
       <c r="B103" t="n">
         <v>80432</v>
@@ -11073,13 +11087,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471158</v>
+        <v>470706</v>
       </c>
       <c r="R103" t="n">
-        <v>6866734</v>
+        <v>6866759</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11134,13 +11148,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389069</t>
+          <t>https://artportalen.se/Sighting/128387487</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128389213</v>
+        <v>128387736</v>
       </c>
       <c r="B104" t="n">
         <v>80432</v>
@@ -11175,10 +11189,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471148</v>
+        <v>470738</v>
       </c>
       <c r="R104" t="n">
-        <v>6866668</v>
+        <v>6866733</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11236,13 +11250,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389213</t>
+          <t>https://artportalen.se/Sighting/128387736</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128389286</v>
+        <v>128389069</v>
       </c>
       <c r="B105" t="n">
         <v>80432</v>
@@ -11277,10 +11291,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471168</v>
+        <v>471158</v>
       </c>
       <c r="R105" t="n">
-        <v>6866647</v>
+        <v>6866734</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11338,13 +11352,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389286</t>
+          <t>https://artportalen.se/Sighting/128389069</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128389420</v>
+        <v>128389213</v>
       </c>
       <c r="B106" t="n">
         <v>80432</v>
@@ -11379,10 +11393,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471185</v>
+        <v>471148</v>
       </c>
       <c r="R106" t="n">
-        <v>6866576</v>
+        <v>6866668</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11440,13 +11454,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389420</t>
+          <t>https://artportalen.se/Sighting/128389213</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128389511</v>
+        <v>128389286</v>
       </c>
       <c r="B107" t="n">
         <v>80432</v>
@@ -11481,10 +11495,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471237</v>
+        <v>471168</v>
       </c>
       <c r="R107" t="n">
-        <v>6866588</v>
+        <v>6866647</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11542,13 +11556,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389511</t>
+          <t>https://artportalen.se/Sighting/128389286</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128389641</v>
+        <v>128389420</v>
       </c>
       <c r="B108" t="n">
         <v>80432</v>
@@ -11583,10 +11597,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471241</v>
+        <v>471185</v>
       </c>
       <c r="R108" t="n">
-        <v>6866656</v>
+        <v>6866576</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11644,13 +11658,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389641</t>
+          <t>https://artportalen.se/Sighting/128389420</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128501347</v>
+        <v>128389511</v>
       </c>
       <c r="B109" t="n">
         <v>80432</v>
@@ -11685,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471275</v>
+        <v>471237</v>
       </c>
       <c r="R109" t="n">
-        <v>6866627</v>
+        <v>6866588</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11715,12 +11729,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11746,13 +11760,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501347</t>
+          <t>https://artportalen.se/Sighting/128389511</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128501744</v>
+        <v>128389641</v>
       </c>
       <c r="B110" t="n">
         <v>80432</v>
@@ -11787,10 +11801,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471288</v>
+        <v>471241</v>
       </c>
       <c r="R110" t="n">
-        <v>6866547</v>
+        <v>6866656</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11817,12 +11831,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11848,13 +11862,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501744</t>
+          <t>https://artportalen.se/Sighting/128389641</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129010715</v>
+        <v>128501347</v>
       </c>
       <c r="B111" t="n">
         <v>80432</v>
@@ -11889,10 +11903,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471061</v>
+        <v>471275</v>
       </c>
       <c r="R111" t="n">
-        <v>6866856</v>
+        <v>6866627</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11919,12 +11933,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11950,16 +11964,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129010715</t>
+          <t>https://artportalen.se/Sighting/128501347</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128375989</v>
+        <v>128501744</v>
       </c>
       <c r="B112" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11967,21 +11981,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11991,10 +12005,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471276</v>
+        <v>471288</v>
       </c>
       <c r="R112" t="n">
-        <v>6866805</v>
+        <v>6866547</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12021,12 +12035,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12052,16 +12066,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375989</t>
+          <t>https://artportalen.se/Sighting/128501744</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128376736</v>
+        <v>129010715</v>
       </c>
       <c r="B113" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12069,21 +12083,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12093,10 +12107,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471282</v>
+        <v>471061</v>
       </c>
       <c r="R113" t="n">
-        <v>6866783</v>
+        <v>6866856</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12123,12 +12137,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12154,13 +12168,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376736</t>
+          <t>https://artportalen.se/Sighting/129010715</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128389351</v>
+        <v>128375989</v>
       </c>
       <c r="B114" t="n">
         <v>78334</v>
@@ -12195,10 +12209,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471215</v>
+        <v>471276</v>
       </c>
       <c r="R114" t="n">
-        <v>6866634</v>
+        <v>6866805</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12225,12 +12239,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12256,16 +12270,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389351</t>
+          <t>https://artportalen.se/Sighting/128375989</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B115" t="n">
-        <v>58114</v>
+        <v>78334</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12273,21 +12287,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12297,13 +12311,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R115" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12333,11 +12347,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12363,16 +12372,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375560</t>
+          <t>https://artportalen.se/Sighting/128376736</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128389855</v>
+        <v>128389351</v>
       </c>
       <c r="B116" t="n">
-        <v>58114</v>
+        <v>78334</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12380,21 +12389,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12404,13 +12413,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471241</v>
+        <v>471215</v>
       </c>
       <c r="R116" t="n">
-        <v>6866622</v>
+        <v>6866634</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12440,11 +12449,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12470,38 +12474,38 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389855</t>
+          <t>https://artportalen.se/Sighting/128389351</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128502866</v>
+        <v>128375560</v>
       </c>
       <c r="B117" t="n">
-        <v>99035</v>
+        <v>58114</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12511,13 +12515,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471139</v>
+        <v>471219</v>
       </c>
       <c r="R117" t="n">
-        <v>6866727</v>
+        <v>6866779</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12541,12 +12545,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12572,63 +12581,54 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502866</t>
+          <t>https://artportalen.se/Sighting/128375560</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128374420</v>
+        <v>128389855</v>
       </c>
       <c r="B118" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471132</v>
+        <v>471241</v>
       </c>
       <c r="R118" t="n">
-        <v>6866856</v>
+        <v>6866622</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12652,12 +12652,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12683,60 +12688,51 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374420</t>
+          <t>https://artportalen.se/Sighting/128389855</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128374436</v>
+        <v>128502866</v>
       </c>
       <c r="B119" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471133</v>
+        <v>471139</v>
       </c>
       <c r="R119" t="n">
-        <v>6866841</v>
+        <v>6866727</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12763,12 +12759,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12794,13 +12790,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374436</t>
+          <t>https://artportalen.se/Sighting/128502866</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128387497</v>
+        <v>128374420</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -12828,17 +12824,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>470693</v>
+        <v>471132</v>
       </c>
       <c r="R120" t="n">
-        <v>6866764</v>
+        <v>6866856</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12865,12 +12870,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12896,13 +12901,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387497</t>
+          <t>https://artportalen.se/Sighting/128374420</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128387629</v>
+        <v>128374436</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -12932,7 +12937,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12946,10 +12951,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>470725</v>
+        <v>471133</v>
       </c>
       <c r="R121" t="n">
-        <v>6866764</v>
+        <v>6866841</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12976,12 +12981,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13007,13 +13012,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387629</t>
+          <t>https://artportalen.se/Sighting/128374436</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128387659</v>
+        <v>128387497</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -13041,26 +13046,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>470734</v>
+        <v>470693</v>
       </c>
       <c r="R122" t="n">
-        <v>6866771</v>
+        <v>6866764</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,13 +13114,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387659</t>
+          <t>https://artportalen.se/Sighting/128387497</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128387695</v>
+        <v>128387629</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -13152,17 +13148,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470733</v>
+        <v>470725</v>
       </c>
       <c r="R123" t="n">
-        <v>6866772</v>
+        <v>6866764</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13220,13 +13225,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387695</t>
+          <t>https://artportalen.se/Sighting/128387629</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128387779</v>
+        <v>128387659</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -13254,17 +13259,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470744</v>
+        <v>470734</v>
       </c>
       <c r="R124" t="n">
-        <v>6866736</v>
+        <v>6866771</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13322,13 +13336,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387779</t>
+          <t>https://artportalen.se/Sighting/128387659</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128387790</v>
+        <v>128387695</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -13363,10 +13377,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470732</v>
+        <v>470733</v>
       </c>
       <c r="R125" t="n">
-        <v>6866727</v>
+        <v>6866772</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13424,13 +13438,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387790</t>
+          <t>https://artportalen.se/Sighting/128387695</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128387936</v>
+        <v>128387779</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -13458,26 +13472,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470750</v>
+        <v>470744</v>
       </c>
       <c r="R126" t="n">
-        <v>6866754</v>
+        <v>6866736</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13535,13 +13540,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387936</t>
+          <t>https://artportalen.se/Sighting/128387779</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128387977</v>
+        <v>128387790</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -13569,26 +13574,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470754</v>
+        <v>470732</v>
       </c>
       <c r="R127" t="n">
-        <v>6866755</v>
+        <v>6866727</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13646,13 +13642,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387977</t>
+          <t>https://artportalen.se/Sighting/128387790</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128388103</v>
+        <v>128387936</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -13680,17 +13676,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470763</v>
+        <v>470750</v>
       </c>
       <c r="R128" t="n">
-        <v>6866753</v>
+        <v>6866754</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13748,13 +13753,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388103</t>
+          <t>https://artportalen.se/Sighting/128387936</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128388228</v>
+        <v>128387977</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -13782,17 +13787,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470788</v>
+        <v>470754</v>
       </c>
       <c r="R129" t="n">
-        <v>6866725</v>
+        <v>6866755</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13850,13 +13864,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388228</t>
+          <t>https://artportalen.se/Sighting/128387977</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128388416</v>
+        <v>128388103</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -13884,26 +13898,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470816</v>
+        <v>470763</v>
       </c>
       <c r="R130" t="n">
-        <v>6866722</v>
+        <v>6866753</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13961,13 +13966,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388416</t>
+          <t>https://artportalen.se/Sighting/128388103</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129010927</v>
+        <v>128388228</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -13995,26 +14000,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>471189</v>
+        <v>470788</v>
       </c>
       <c r="R131" t="n">
-        <v>6866691</v>
+        <v>6866725</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14041,12 +14037,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14072,13 +14068,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129010927</t>
+          <t>https://artportalen.se/Sighting/128388228</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129012279</v>
+        <v>128388416</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -14122,10 +14118,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470794</v>
+        <v>470816</v>
       </c>
       <c r="R132" t="n">
-        <v>6866768</v>
+        <v>6866722</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14152,12 +14148,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14183,51 +14179,60 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129012279</t>
+          <t>https://artportalen.se/Sighting/128388416</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128375794</v>
+        <v>129010927</v>
       </c>
       <c r="B133" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471241</v>
+        <v>471189</v>
       </c>
       <c r="R133" t="n">
-        <v>6866786</v>
+        <v>6866691</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14254,12 +14259,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14285,51 +14290,60 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375794</t>
+          <t>https://artportalen.se/Sighting/129010927</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128375924</v>
+        <v>129012279</v>
       </c>
       <c r="B134" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471255</v>
+        <v>470794</v>
       </c>
       <c r="R134" t="n">
-        <v>6866786</v>
+        <v>6866768</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14356,12 +14370,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14387,13 +14401,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375924</t>
+          <t>https://artportalen.se/Sighting/129012279</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128376197</v>
+        <v>128375794</v>
       </c>
       <c r="B135" t="n">
         <v>79085</v>
@@ -14428,10 +14442,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471280</v>
+        <v>471241</v>
       </c>
       <c r="R135" t="n">
-        <v>6866807</v>
+        <v>6866786</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14489,13 +14503,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376197</t>
+          <t>https://artportalen.se/Sighting/128375794</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128376574</v>
+        <v>128375924</v>
       </c>
       <c r="B136" t="n">
         <v>79085</v>
@@ -14530,13 +14544,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471364</v>
+        <v>471255</v>
       </c>
       <c r="R136" t="n">
-        <v>6866709</v>
+        <v>6866786</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14591,13 +14605,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376574</t>
+          <t>https://artportalen.se/Sighting/128375924</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128387828</v>
+        <v>128376197</v>
       </c>
       <c r="B137" t="n">
         <v>79085</v>
@@ -14632,13 +14646,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470743</v>
+        <v>471280</v>
       </c>
       <c r="R137" t="n">
-        <v>6866698</v>
+        <v>6866807</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14662,12 +14676,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14693,13 +14707,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387828</t>
+          <t>https://artportalen.se/Sighting/128376197</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128388053</v>
+        <v>128376574</v>
       </c>
       <c r="B138" t="n">
         <v>79085</v>
@@ -14734,10 +14748,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470770</v>
+        <v>471364</v>
       </c>
       <c r="R138" t="n">
-        <v>6866780</v>
+        <v>6866709</v>
       </c>
       <c r="S138" t="n">
         <v>20</v>
@@ -14764,12 +14778,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14795,13 +14809,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388053</t>
+          <t>https://artportalen.se/Sighting/128376574</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128389403</v>
+        <v>128387828</v>
       </c>
       <c r="B139" t="n">
         <v>79085</v>
@@ -14836,13 +14850,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471187</v>
+        <v>470743</v>
       </c>
       <c r="R139" t="n">
-        <v>6866586</v>
+        <v>6866698</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14897,13 +14911,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389403</t>
+          <t>https://artportalen.se/Sighting/128387828</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128501144</v>
+        <v>128388053</v>
       </c>
       <c r="B140" t="n">
         <v>79085</v>
@@ -14938,13 +14952,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>471257</v>
+        <v>470770</v>
       </c>
       <c r="R140" t="n">
-        <v>6866697</v>
+        <v>6866780</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14968,12 +14982,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14999,13 +15013,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501144</t>
+          <t>https://artportalen.se/Sighting/128388053</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128502309</v>
+        <v>128389403</v>
       </c>
       <c r="B141" t="n">
         <v>79085</v>
@@ -15040,10 +15054,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471311</v>
+        <v>471187</v>
       </c>
       <c r="R141" t="n">
-        <v>6866598</v>
+        <v>6866586</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15070,12 +15084,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15101,16 +15115,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502309</t>
+          <t>https://artportalen.se/Sighting/128389403</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128376712</v>
+        <v>128501144</v>
       </c>
       <c r="B142" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15118,21 +15132,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15142,10 +15156,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471282</v>
+        <v>471257</v>
       </c>
       <c r="R142" t="n">
-        <v>6866780</v>
+        <v>6866697</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15172,12 +15186,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15203,16 +15217,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376712</t>
+          <t>https://artportalen.se/Sighting/128501144</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128389324</v>
+        <v>128502309</v>
       </c>
       <c r="B143" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15220,21 +15234,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15244,10 +15258,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471177</v>
+        <v>471311</v>
       </c>
       <c r="R143" t="n">
-        <v>6866639</v>
+        <v>6866598</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15274,12 +15288,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15305,13 +15319,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389324</t>
+          <t>https://artportalen.se/Sighting/128502309</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128502577</v>
+        <v>128376712</v>
       </c>
       <c r="B144" t="n">
         <v>79917</v>
@@ -15346,10 +15360,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471347</v>
+        <v>471282</v>
       </c>
       <c r="R144" t="n">
-        <v>6866673</v>
+        <v>6866780</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15376,12 +15390,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15406,6 +15420,210 @@
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376712</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128389324</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>471177</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6866639</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389324</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128502577</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6866673</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128502577</t>
         </is>
@@ -15556,6 +15774,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ146"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9624,32 +9624,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128376702</v>
+        <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>78730</v>
+        <v>79476</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471287</v>
+        <v>470780</v>
       </c>
       <c r="R89" t="n">
-        <v>6866773</v>
+        <v>6866735</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9720,16 +9720,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376702</t>
+          <t>https://artportalen.se/Sighting/136764548</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128374470</v>
+        <v>128376702</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9737,21 +9737,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9761,13 +9761,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471139</v>
+        <v>471287</v>
       </c>
       <c r="R90" t="n">
-        <v>6866835</v>
+        <v>6866773</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9822,13 +9822,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374470</t>
+          <t>https://artportalen.se/Sighting/128376702</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128388207</v>
+        <v>128374470</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -9863,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>470789</v>
+        <v>471139</v>
       </c>
       <c r="R91" t="n">
-        <v>6866739</v>
+        <v>6866835</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9924,13 +9924,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388207</t>
+          <t>https://artportalen.se/Sighting/128374470</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128389187</v>
+        <v>128388207</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -9965,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471196</v>
+        <v>470789</v>
       </c>
       <c r="R92" t="n">
-        <v>6866706</v>
+        <v>6866739</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10026,13 +10026,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389187</t>
+          <t>https://artportalen.se/Sighting/128388207</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128389329</v>
+        <v>128389187</v>
       </c>
       <c r="B93" t="n">
         <v>79084</v>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471172</v>
+        <v>471196</v>
       </c>
       <c r="R93" t="n">
-        <v>6866632</v>
+        <v>6866706</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10128,13 +10128,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389329</t>
+          <t>https://artportalen.se/Sighting/128389187</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128501083</v>
+        <v>128389329</v>
       </c>
       <c r="B94" t="n">
         <v>79084</v>
@@ -10169,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471219</v>
+        <v>471172</v>
       </c>
       <c r="R94" t="n">
-        <v>6866725</v>
+        <v>6866632</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10230,13 +10230,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501083</t>
+          <t>https://artportalen.se/Sighting/128389329</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128501209</v>
+        <v>128501083</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -10271,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471244</v>
+        <v>471219</v>
       </c>
       <c r="R95" t="n">
-        <v>6866687</v>
+        <v>6866725</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10332,13 +10332,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501209</t>
+          <t>https://artportalen.se/Sighting/128501083</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128502509</v>
+        <v>128501209</v>
       </c>
       <c r="B96" t="n">
         <v>79084</v>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471315</v>
+        <v>471244</v>
       </c>
       <c r="R96" t="n">
-        <v>6866670</v>
+        <v>6866687</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10434,13 +10434,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502509</t>
+          <t>https://artportalen.se/Sighting/128501209</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128502607</v>
+        <v>128502509</v>
       </c>
       <c r="B97" t="n">
         <v>79084</v>
@@ -10475,10 +10475,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471349</v>
+        <v>471315</v>
       </c>
       <c r="R97" t="n">
-        <v>6866695</v>
+        <v>6866670</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,16 +10536,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502607</t>
+          <t>https://artportalen.se/Sighting/128502509</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128373940</v>
+        <v>128502607</v>
       </c>
       <c r="B98" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10553,21 +10553,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10577,10 +10577,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471083</v>
+        <v>471349</v>
       </c>
       <c r="R98" t="n">
-        <v>6866852</v>
+        <v>6866695</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10638,16 +10638,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128373940</t>
+          <t>https://artportalen.se/Sighting/128502607</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128373989</v>
+        <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80432</v>
+        <v>80095</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10679,13 +10679,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471102</v>
+        <v>470813</v>
       </c>
       <c r="R99" t="n">
-        <v>6866857</v>
+        <v>6866726</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10740,13 +10740,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128373989</t>
+          <t>https://artportalen.se/Sighting/136764258</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128387227</v>
+        <v>128373940</v>
       </c>
       <c r="B100" t="n">
         <v>80432</v>
@@ -10781,10 +10781,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>470551</v>
+        <v>471083</v>
       </c>
       <c r="R100" t="n">
-        <v>6866892</v>
+        <v>6866852</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10811,12 +10811,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10842,13 +10842,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387227</t>
+          <t>https://artportalen.se/Sighting/128373940</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128387286</v>
+        <v>128373989</v>
       </c>
       <c r="B101" t="n">
         <v>80432</v>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>470551</v>
+        <v>471102</v>
       </c>
       <c r="R101" t="n">
-        <v>6866872</v>
+        <v>6866857</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10944,13 +10944,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387286</t>
+          <t>https://artportalen.se/Sighting/128373989</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128387292</v>
+        <v>128387227</v>
       </c>
       <c r="B102" t="n">
         <v>80432</v>
@@ -10988,7 +10988,7 @@
         <v>470551</v>
       </c>
       <c r="R102" t="n">
-        <v>6866868</v>
+        <v>6866892</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11046,13 +11046,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387292</t>
+          <t>https://artportalen.se/Sighting/128387227</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128387487</v>
+        <v>128387286</v>
       </c>
       <c r="B103" t="n">
         <v>80432</v>
@@ -11087,13 +11087,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>470706</v>
+        <v>470551</v>
       </c>
       <c r="R103" t="n">
-        <v>6866759</v>
+        <v>6866872</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11148,13 +11148,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387487</t>
+          <t>https://artportalen.se/Sighting/128387286</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128387736</v>
+        <v>128387292</v>
       </c>
       <c r="B104" t="n">
         <v>80432</v>
@@ -11189,10 +11189,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>470738</v>
+        <v>470551</v>
       </c>
       <c r="R104" t="n">
-        <v>6866733</v>
+        <v>6866868</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,13 +11250,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387736</t>
+          <t>https://artportalen.se/Sighting/128387292</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128389069</v>
+        <v>128387487</v>
       </c>
       <c r="B105" t="n">
         <v>80432</v>
@@ -11291,13 +11291,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471158</v>
+        <v>470706</v>
       </c>
       <c r="R105" t="n">
-        <v>6866734</v>
+        <v>6866759</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11352,13 +11352,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389069</t>
+          <t>https://artportalen.se/Sighting/128387487</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128389213</v>
+        <v>128387736</v>
       </c>
       <c r="B106" t="n">
         <v>80432</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471148</v>
+        <v>470738</v>
       </c>
       <c r="R106" t="n">
-        <v>6866668</v>
+        <v>6866733</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,13 +11454,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389213</t>
+          <t>https://artportalen.se/Sighting/128387736</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128389286</v>
+        <v>128389069</v>
       </c>
       <c r="B107" t="n">
         <v>80432</v>
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471168</v>
+        <v>471158</v>
       </c>
       <c r="R107" t="n">
-        <v>6866647</v>
+        <v>6866734</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,13 +11556,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389286</t>
+          <t>https://artportalen.se/Sighting/128389069</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128389420</v>
+        <v>128389213</v>
       </c>
       <c r="B108" t="n">
         <v>80432</v>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471185</v>
+        <v>471148</v>
       </c>
       <c r="R108" t="n">
-        <v>6866576</v>
+        <v>6866668</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11658,13 +11658,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389420</t>
+          <t>https://artportalen.se/Sighting/128389213</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128389511</v>
+        <v>128389286</v>
       </c>
       <c r="B109" t="n">
         <v>80432</v>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471237</v>
+        <v>471168</v>
       </c>
       <c r="R109" t="n">
-        <v>6866588</v>
+        <v>6866647</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11760,13 +11760,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389511</t>
+          <t>https://artportalen.se/Sighting/128389286</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128389641</v>
+        <v>128389420</v>
       </c>
       <c r="B110" t="n">
         <v>80432</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471241</v>
+        <v>471185</v>
       </c>
       <c r="R110" t="n">
-        <v>6866656</v>
+        <v>6866576</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11862,13 +11862,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389641</t>
+          <t>https://artportalen.se/Sighting/128389420</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128501347</v>
+        <v>128389511</v>
       </c>
       <c r="B111" t="n">
         <v>80432</v>
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471275</v>
+        <v>471237</v>
       </c>
       <c r="R111" t="n">
-        <v>6866627</v>
+        <v>6866588</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11933,12 +11933,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11964,13 +11964,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501347</t>
+          <t>https://artportalen.se/Sighting/128389511</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128501744</v>
+        <v>128389641</v>
       </c>
       <c r="B112" t="n">
         <v>80432</v>
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471288</v>
+        <v>471241</v>
       </c>
       <c r="R112" t="n">
-        <v>6866547</v>
+        <v>6866656</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12035,12 +12035,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12066,13 +12066,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501744</t>
+          <t>https://artportalen.se/Sighting/128389641</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129010715</v>
+        <v>128501347</v>
       </c>
       <c r="B113" t="n">
         <v>80432</v>
@@ -12107,10 +12107,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471061</v>
+        <v>471275</v>
       </c>
       <c r="R113" t="n">
-        <v>6866856</v>
+        <v>6866627</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12168,16 +12168,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129010715</t>
+          <t>https://artportalen.se/Sighting/128501347</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128375989</v>
+        <v>128501744</v>
       </c>
       <c r="B114" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12185,21 +12185,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12209,10 +12209,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471276</v>
+        <v>471288</v>
       </c>
       <c r="R114" t="n">
-        <v>6866805</v>
+        <v>6866547</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12270,16 +12270,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375989</t>
+          <t>https://artportalen.se/Sighting/128501744</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128376736</v>
+        <v>129010715</v>
       </c>
       <c r="B115" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12287,21 +12287,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12311,10 +12311,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471282</v>
+        <v>471061</v>
       </c>
       <c r="R115" t="n">
-        <v>6866783</v>
+        <v>6866856</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12372,13 +12372,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376736</t>
+          <t>https://artportalen.se/Sighting/129010715</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128389351</v>
+        <v>128375989</v>
       </c>
       <c r="B116" t="n">
         <v>78334</v>
@@ -12413,10 +12413,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471215</v>
+        <v>471276</v>
       </c>
       <c r="R116" t="n">
-        <v>6866634</v>
+        <v>6866805</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12474,16 +12474,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389351</t>
+          <t>https://artportalen.se/Sighting/128375989</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128375560</v>
+        <v>128376736</v>
       </c>
       <c r="B117" t="n">
-        <v>58114</v>
+        <v>78334</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471219</v>
+        <v>471282</v>
       </c>
       <c r="R117" t="n">
-        <v>6866779</v>
+        <v>6866783</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12551,11 +12551,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12581,16 +12576,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375560</t>
+          <t>https://artportalen.se/Sighting/128376736</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128389855</v>
+        <v>128389351</v>
       </c>
       <c r="B118" t="n">
-        <v>58114</v>
+        <v>78334</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12598,21 +12593,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12622,13 +12617,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471241</v>
+        <v>471215</v>
       </c>
       <c r="R118" t="n">
-        <v>6866622</v>
+        <v>6866634</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12658,11 +12653,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12688,38 +12678,38 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389855</t>
+          <t>https://artportalen.se/Sighting/128389351</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128502866</v>
+        <v>128375560</v>
       </c>
       <c r="B119" t="n">
-        <v>99035</v>
+        <v>58114</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12729,13 +12719,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471139</v>
+        <v>471219</v>
       </c>
       <c r="R119" t="n">
-        <v>6866727</v>
+        <v>6866779</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12759,12 +12749,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Läte från talltitor.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12790,63 +12785,54 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502866</t>
+          <t>https://artportalen.se/Sighting/128375560</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128374420</v>
+        <v>128389855</v>
       </c>
       <c r="B120" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471132</v>
+        <v>471241</v>
       </c>
       <c r="R120" t="n">
-        <v>6866856</v>
+        <v>6866622</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12870,12 +12856,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Noterat läten.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12901,60 +12892,51 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374420</t>
+          <t>https://artportalen.se/Sighting/128389855</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128374436</v>
+        <v>128502866</v>
       </c>
       <c r="B121" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471133</v>
+        <v>471139</v>
       </c>
       <c r="R121" t="n">
-        <v>6866841</v>
+        <v>6866727</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12981,12 +12963,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13012,13 +12994,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128374436</t>
+          <t>https://artportalen.se/Sighting/128502866</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128387497</v>
+        <v>128374420</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -13046,17 +13028,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>470693</v>
+        <v>471132</v>
       </c>
       <c r="R122" t="n">
-        <v>6866764</v>
+        <v>6866856</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13083,12 +13074,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13114,13 +13105,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387497</t>
+          <t>https://artportalen.se/Sighting/128374420</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128387629</v>
+        <v>128374436</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -13150,7 +13141,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13164,10 +13155,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470725</v>
+        <v>471133</v>
       </c>
       <c r="R123" t="n">
-        <v>6866764</v>
+        <v>6866841</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,12 +13185,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13225,13 +13216,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387629</t>
+          <t>https://artportalen.se/Sighting/128374436</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128387659</v>
+        <v>128387497</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -13259,26 +13250,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470734</v>
+        <v>470693</v>
       </c>
       <c r="R124" t="n">
-        <v>6866771</v>
+        <v>6866764</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13336,13 +13318,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387659</t>
+          <t>https://artportalen.se/Sighting/128387497</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128387695</v>
+        <v>128387629</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -13370,17 +13352,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470733</v>
+        <v>470725</v>
       </c>
       <c r="R125" t="n">
-        <v>6866772</v>
+        <v>6866764</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13438,13 +13429,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387695</t>
+          <t>https://artportalen.se/Sighting/128387629</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128387779</v>
+        <v>128387659</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -13472,17 +13463,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470744</v>
+        <v>470734</v>
       </c>
       <c r="R126" t="n">
-        <v>6866736</v>
+        <v>6866771</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13540,13 +13540,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387779</t>
+          <t>https://artportalen.se/Sighting/128387659</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128387790</v>
+        <v>128387695</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -13581,10 +13581,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470732</v>
+        <v>470733</v>
       </c>
       <c r="R127" t="n">
-        <v>6866727</v>
+        <v>6866772</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13642,13 +13642,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387790</t>
+          <t>https://artportalen.se/Sighting/128387695</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128387936</v>
+        <v>128387779</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -13676,26 +13676,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470750</v>
+        <v>470744</v>
       </c>
       <c r="R128" t="n">
-        <v>6866754</v>
+        <v>6866736</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13753,13 +13744,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387936</t>
+          <t>https://artportalen.se/Sighting/128387779</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128387977</v>
+        <v>128387790</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -13787,26 +13778,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470754</v>
+        <v>470732</v>
       </c>
       <c r="R129" t="n">
-        <v>6866755</v>
+        <v>6866727</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13864,13 +13846,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387977</t>
+          <t>https://artportalen.se/Sighting/128387790</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128388103</v>
+        <v>128387936</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -13898,17 +13880,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470763</v>
+        <v>470750</v>
       </c>
       <c r="R130" t="n">
-        <v>6866753</v>
+        <v>6866754</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13966,13 +13957,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388103</t>
+          <t>https://artportalen.se/Sighting/128387936</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128388228</v>
+        <v>128387977</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -14000,17 +13991,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470788</v>
+        <v>470754</v>
       </c>
       <c r="R131" t="n">
-        <v>6866725</v>
+        <v>6866755</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14068,13 +14068,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388228</t>
+          <t>https://artportalen.se/Sighting/128387977</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128388416</v>
+        <v>128388103</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -14102,26 +14102,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470816</v>
+        <v>470763</v>
       </c>
       <c r="R132" t="n">
-        <v>6866722</v>
+        <v>6866753</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14179,13 +14170,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388416</t>
+          <t>https://artportalen.se/Sighting/128388103</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129010927</v>
+        <v>128388228</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -14213,26 +14204,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471189</v>
+        <v>470788</v>
       </c>
       <c r="R133" t="n">
-        <v>6866691</v>
+        <v>6866725</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14259,12 +14241,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14290,13 +14272,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129010927</t>
+          <t>https://artportalen.se/Sighting/128388228</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129012279</v>
+        <v>128388416</v>
       </c>
       <c r="B134" t="n">
         <v>99118</v>
@@ -14340,10 +14322,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470794</v>
+        <v>470816</v>
       </c>
       <c r="R134" t="n">
-        <v>6866768</v>
+        <v>6866722</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14370,12 +14352,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14401,51 +14383,60 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129012279</t>
+          <t>https://artportalen.se/Sighting/128388416</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128375794</v>
+        <v>129010927</v>
       </c>
       <c r="B135" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471241</v>
+        <v>471189</v>
       </c>
       <c r="R135" t="n">
-        <v>6866786</v>
+        <v>6866691</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14472,12 +14463,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14503,51 +14494,60 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375794</t>
+          <t>https://artportalen.se/Sighting/129010927</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128375924</v>
+        <v>129012279</v>
       </c>
       <c r="B136" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471255</v>
+        <v>470794</v>
       </c>
       <c r="R136" t="n">
-        <v>6866786</v>
+        <v>6866768</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14574,12 +14574,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14605,13 +14605,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128375924</t>
+          <t>https://artportalen.se/Sighting/129012279</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128376197</v>
+        <v>128375794</v>
       </c>
       <c r="B137" t="n">
         <v>79085</v>
@@ -14646,10 +14646,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471280</v>
+        <v>471241</v>
       </c>
       <c r="R137" t="n">
-        <v>6866807</v>
+        <v>6866786</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14707,13 +14707,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376197</t>
+          <t>https://artportalen.se/Sighting/128375794</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128376574</v>
+        <v>128375924</v>
       </c>
       <c r="B138" t="n">
         <v>79085</v>
@@ -14748,13 +14748,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>471364</v>
+        <v>471255</v>
       </c>
       <c r="R138" t="n">
-        <v>6866709</v>
+        <v>6866786</v>
       </c>
       <c r="S138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14809,13 +14809,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376574</t>
+          <t>https://artportalen.se/Sighting/128375924</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128387828</v>
+        <v>128376197</v>
       </c>
       <c r="B139" t="n">
         <v>79085</v>
@@ -14850,13 +14850,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470743</v>
+        <v>471280</v>
       </c>
       <c r="R139" t="n">
-        <v>6866698</v>
+        <v>6866807</v>
       </c>
       <c r="S139" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14880,12 +14880,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14911,13 +14911,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128387828</t>
+          <t>https://artportalen.se/Sighting/128376197</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128388053</v>
+        <v>128376574</v>
       </c>
       <c r="B140" t="n">
         <v>79085</v>
@@ -14952,10 +14952,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470770</v>
+        <v>471364</v>
       </c>
       <c r="R140" t="n">
-        <v>6866780</v>
+        <v>6866709</v>
       </c>
       <c r="S140" t="n">
         <v>20</v>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15013,13 +15013,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128388053</t>
+          <t>https://artportalen.se/Sighting/128376574</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128389403</v>
+        <v>128387828</v>
       </c>
       <c r="B141" t="n">
         <v>79085</v>
@@ -15054,13 +15054,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471187</v>
+        <v>470743</v>
       </c>
       <c r="R141" t="n">
-        <v>6866586</v>
+        <v>6866698</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15115,13 +15115,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389403</t>
+          <t>https://artportalen.se/Sighting/128387828</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128501144</v>
+        <v>128388053</v>
       </c>
       <c r="B142" t="n">
         <v>79085</v>
@@ -15156,13 +15156,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471257</v>
+        <v>470770</v>
       </c>
       <c r="R142" t="n">
-        <v>6866697</v>
+        <v>6866780</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15186,12 +15186,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15217,13 +15217,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128501144</t>
+          <t>https://artportalen.se/Sighting/128388053</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128502309</v>
+        <v>128389403</v>
       </c>
       <c r="B143" t="n">
         <v>79085</v>
@@ -15258,10 +15258,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>471311</v>
+        <v>471187</v>
       </c>
       <c r="R143" t="n">
-        <v>6866598</v>
+        <v>6866586</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15288,12 +15288,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15319,16 +15319,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128502309</t>
+          <t>https://artportalen.se/Sighting/128389403</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128376712</v>
+        <v>128501144</v>
       </c>
       <c r="B144" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15336,21 +15336,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15360,10 +15360,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471282</v>
+        <v>471257</v>
       </c>
       <c r="R144" t="n">
-        <v>6866780</v>
+        <v>6866697</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15390,12 +15390,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15421,16 +15421,16 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128376712</t>
+          <t>https://artportalen.se/Sighting/128501144</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128389324</v>
+        <v>128502309</v>
       </c>
       <c r="B145" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15438,21 +15438,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15462,10 +15462,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471177</v>
+        <v>471311</v>
       </c>
       <c r="R145" t="n">
-        <v>6866639</v>
+        <v>6866598</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15492,12 +15492,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15523,13 +15523,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128389324</t>
+          <t>https://artportalen.se/Sighting/128502309</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128502577</v>
+        <v>128376712</v>
       </c>
       <c r="B146" t="n">
         <v>79917</v>
@@ -15564,10 +15564,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471347</v>
+        <v>471282</v>
       </c>
       <c r="R146" t="n">
-        <v>6866673</v>
+        <v>6866780</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15624,6 +15624,210 @@
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128376712</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128389324</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>471177</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6866639</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128389324</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128502577</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>471347</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6866673</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128502577</t>
         </is>
@@ -15776,6 +15980,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -2723,7 +2723,7 @@
         <v>136684899</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4223,11 +4223,7 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sålnberget, Sålnberget, Hjd</t>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -4188,7 +4188,7 @@
         <v>136684295</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -9623,7 +9623,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 136-2025 artfynd.xlsx
+++ b/artfynd/A 136-2025 artfynd.xlsx
@@ -9623,7 +9623,7 @@
         <v>136764548</v>
       </c>
       <c r="B89" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>136764258</v>
       </c>
       <c r="B99" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
